--- a/docs/plan-scaling-date.xlsx
+++ b/docs/plan-scaling-date.xlsx
@@ -60,7 +60,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +80,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -138,13 +143,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -234,7 +241,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Capital financé total</a:t>
+              <a:t>Capital financé (validé)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -248,7 +255,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Plan mensuel'!F1</f>
+              <f>'Plan mensuel'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -266,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Plan mensuel'!$A$2:$A$5</f>
+              <f>'Plan mensuel'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Plan mensuel'!$F$2:$F$5</f>
+              <f>'Plan mensuel'!$D$2:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -351,7 +358,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Plan mensuel'!I1</f>
+              <f>'Plan mensuel'!H1</f>
             </strRef>
           </tx>
           <spPr>
@@ -369,12 +376,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Plan mensuel'!$A$2:$A$5</f>
+              <f>'Plan mensuel'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Plan mensuel'!$I$2:$I$5</f>
+              <f>'Plan mensuel'!$H$2:$H$9</f>
             </numRef>
           </val>
         </ser>
@@ -766,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="116" customWidth="1" min="1" max="1"/>
@@ -775,7 +782,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Plan de scaling daté — maximum de firmes par mois</t>
+          <t>Plan de scaling daté — avec temps de validation des étapes</t>
         </is>
       </c>
     </row>
@@ -795,76 +802,97 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>VOTRE MÉTHODE</t>
+          <t>VOTRE MÉTHODE + TEMPS DE VALIDATION</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>01 octobre 2026 : compte direct FundedNext 10 000 $. Fin octobre, payout 10 % = 1 000 $, moins 30 % firme = 700 $.</t>
+          <t>01 octobre 2026 : compte direct FundedNext 10 000 $. Fin octobre, payout 10 % = 1 000 $, moins 30 % = 700 $.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Chaque mois, avec tout l'argent disponible, vous achetez le MAXIMUM de firmes possible (pas une seule) : on prend le plus gros capital d'abord, firmes CFD en MetaTrader 5, puis autres CFD, puis Futures, chacune une seule fois. Le reste du payout est votre salaire.</t>
+          <t>Chaque mois, tout l'argent disponible achète le maximum de firmes (plus gros capital d'abord ; CFD MetaTrader 5, puis CFD, puis Futures ; chacune une fois).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Dans ce scénario (10 % / 30 %), les 189 firmes (≈ 113 M$) sont toutes acquises dès janvier 2027.</t>
+          <t>Comptes DIRECTS / INSTANT : financés immédiatement, ils rapportent dès la fin du mois d'achat.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Comptes À ÉTAPES : il faut d'abord valider l'évaluation, à raison de 10 % par mois. Un objectif de 10 % prend 1 mois, 5 % prend une demi-mois. Un 2 étapes 10 %+5 % met donc 1,5 mois à être financé, et ne rapporte qu'ensuite. La durée exacte est dans l'onglet Détail (colonne Durée d'évaluation) et sa date de financement.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>LES ONGLETS</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Ce classeur couvre toutes les firmes conformes (CFD puis Futures).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Plan mensuel : une ligne par mois (date en lettres), nombre de firmes achetées, capital ajouté, capital total, payout brut, part firme, salaire net, trésorerie.</t>
+          <t>Dans ce scénario (10 % / 30 %), la dernière firme est financée vers le 01 mai 2027.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Détail des achats : une ligne par firme achetée, avec sa date, son cycle, sa plateforme, MT5 ou non, son capital et son prix.</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Paramètres / Graphiques.</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>LES ONGLETS</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Plan mensuel : date en lettres, firmes achetées, capital financé (déjà validé), capital en cours d'évaluation, payout brut, part firme, salaire net, trésorerie.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>NOTE</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Détail des achats : chaque firme, sa date d'achat, son type, sa durée d'évaluation et sa date de financement.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>L'ordre et le calendrier des achats sont calculés pour le scénario 10 %/30 %. Les colonnes d'argent sont des formules : changez le payout ou la part firme et salaire, part firme et trésorerie se recalculent. Prix hors codes promo. Borne théorique sans échec d'évaluation ni plafond de retrait.</t>
+          <t>Paramètres / Graphiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Ordre et calendrier calculés pour 10 %/30 %. Colonnes d'argent en formules. Prix hors codes promo. Borne théorique sans échec d'évaluation ni plafond de retrait.</t>
         </is>
       </c>
     </row>
@@ -934,20 +962,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -968,37 +996,37 @@
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>Capital ajouté ($)</t>
+          <t>Capital financé (validé) ($)</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>Prix payé ($)</t>
+          <t>Capital en évaluation ($)</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>Capital financé total ($)</t>
+          <t>Payout brut ($)</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>Payout brut ($)</t>
+          <t>Part firme ($)</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>Part firme ($)</t>
+          <t>Salaire net ($)</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>Salaire net ($)</t>
+          <t>Trésorerie ($)</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>Trésorerie ($)</t>
+          <t>Comptes financés</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
@@ -1022,29 +1050,29 @@
         <v>1</v>
       </c>
       <c r="D2" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E2" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G2" s="10">
-        <f>F2*Paramètres!$B$3</f>
+      <c r="F2" s="12">
+        <f>D2*Paramètres!$B$3</f>
         <v/>
       </c>
+      <c r="G2" s="12">
+        <f>F2*Paramètres!$B$4</f>
+        <v/>
+      </c>
       <c r="H2" s="10">
-        <f>G2*Paramètres!$B$4</f>
+        <f>F2-G2</f>
         <v/>
       </c>
-      <c r="I2" s="11">
-        <f>G2-H2</f>
+      <c r="I2" s="12">
+        <f>H2-0</f>
         <v/>
       </c>
-      <c r="J2" s="10">
-        <f>I2-E2</f>
-        <v/>
+      <c r="J2" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="K2" s="9" t="n">
         <v>1</v>
@@ -1065,29 +1093,29 @@
         <v>3</v>
       </c>
       <c r="D3" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E3" s="11" t="n">
         <v>325000</v>
       </c>
-      <c r="E3" s="10" t="n">
-        <v>656</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>335000</v>
-      </c>
-      <c r="G3" s="10">
-        <f>F3*Paramètres!$B$3</f>
+      <c r="F3" s="12">
+        <f>D3*Paramètres!$B$3</f>
         <v/>
       </c>
+      <c r="G3" s="12">
+        <f>F3*Paramètres!$B$4</f>
+        <v/>
+      </c>
       <c r="H3" s="10">
-        <f>G3*Paramètres!$B$4</f>
+        <f>F3-G3</f>
         <v/>
       </c>
-      <c r="I3" s="11">
-        <f>G3-H3</f>
+      <c r="I3" s="12">
+        <f>I2+H3-656</f>
         <v/>
       </c>
-      <c r="J3" s="10">
-        <f>J2+I3-E3</f>
-        <v/>
+      <c r="J3" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>4</v>
@@ -1101,39 +1129,39 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>PaidPex; Lux Trading Firm; Elysium Forex; Hydra Futures; The5ers Crypto; Real Trader Fund … (+1)</t>
+          <t>FundedCobra; The5ers Crypto</t>
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>12723000</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>23467</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>13058000</v>
-      </c>
-      <c r="G4" s="10">
-        <f>F4*Paramètres!$B$3</f>
+        <v>335000</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>320000</v>
+      </c>
+      <c r="F4" s="12">
+        <f>D4*Paramètres!$B$3</f>
         <v/>
       </c>
+      <c r="G4" s="12">
+        <f>F4*Paramètres!$B$4</f>
+        <v/>
+      </c>
       <c r="H4" s="10">
-        <f>G4*Paramètres!$B$4</f>
+        <f>F4-G4</f>
         <v/>
       </c>
-      <c r="I4" s="11">
-        <f>G4-H4</f>
+      <c r="I4" s="12">
+        <f>I3+H4-711</f>
         <v/>
       </c>
-      <c r="J4" s="10">
-        <f>J3+I4-E4</f>
-        <v/>
+      <c r="J4" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -1144,38 +1172,202 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Upcomers; NairaProp; The Whale Order; NairaFunded; Finotive Funding; XLTrade … (+173)</t>
+          <t>PaidPex; Lux Trading Firm; The Whale Order; Hydra Futures</t>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>100132540</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>814982</v>
-      </c>
-      <c r="F5" s="11" t="n">
+        <v>1035000</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>13120000</v>
+      </c>
+      <c r="F5" s="12">
+        <f>D5*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="G5" s="12">
+        <f>F5*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="H5" s="10">
+        <f>F5-G5</f>
+        <v/>
+      </c>
+      <c r="I5" s="12">
+        <f>I4+H5-32935</f>
+        <v/>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>01 février 2027</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Upcomers; NairaFunded; Elysium Forex; XLTrade</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>19155000</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="F6" s="12">
+        <f>D6*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="12">
+        <f>F6*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="H6" s="10">
+        <f>F6-G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="12">
+        <f>I5+H6-95963</f>
+        <v/>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>NairaProp; Finotive Funding; Funded Traders Pro; IQ Capital; Funded Trader Markets; Space Funded … (+170)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>176</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>32735000</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>80455540</v>
+      </c>
+      <c r="F7" s="12">
+        <f>D7*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>F7*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="H7" s="10">
+        <f>F7-G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="12">
+        <f>I6+H7-708840</f>
+        <v/>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr"/>
+      <c r="C8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>108590540</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="F8" s="12">
+        <f>D8*Paramètres!$B$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>F8*Paramètres!$B$4</f>
+        <v/>
+      </c>
+      <c r="H8" s="10">
+        <f>F8-G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="12">
+        <f>I7+H8-0</f>
+        <v/>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>183</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>01 mai 2027</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr"/>
+      <c r="C9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10" t="n">
         <v>113190540</v>
       </c>
-      <c r="G5" s="10">
-        <f>F5*Paramètres!$B$3</f>
+      <c r="E9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
+        <f>D9*Paramètres!$B$3</f>
         <v/>
       </c>
-      <c r="H5" s="10">
-        <f>G5*Paramètres!$B$4</f>
+      <c r="G9" s="12">
+        <f>F9*Paramètres!$B$4</f>
         <v/>
       </c>
-      <c r="I5" s="11">
-        <f>G5-H5</f>
+      <c r="H9" s="10">
+        <f>F9-G9</f>
         <v/>
       </c>
-      <c r="J5" s="10">
-        <f>J4+I5-E5</f>
+      <c r="I9" s="12">
+        <f>I8+H9-0</f>
         <v/>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="J9" s="9" t="n">
+        <v>190</v>
+      </c>
+      <c r="K9" s="9" t="n">
         <v>190</v>
       </c>
     </row>
@@ -1190,50 +1382,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:J190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Date d'achat</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Cycle</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Prop firm</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Plateforme</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
-        <is>
-          <t>MetaTrader 5 ?</t>
-        </is>
-      </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>MT5 ?</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Durée évaluation (mois)</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Date de financement</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Capital ($)</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Prix ($)</t>
         </is>
@@ -1245,7 +1455,7 @@
           <t>01 novembre 2026</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -1265,10 +1475,23 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>01 décembre 2026</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="J2" s="12" t="n">
         <v>514</v>
       </c>
     </row>
@@ -1278,7 +1501,7 @@
           <t>01 novembre 2026</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -1298,10 +1521,23 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F3" s="10" t="n">
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>19 décembre 2026</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="n">
         <v>120000</v>
       </c>
-      <c r="G3" s="10" t="n">
+      <c r="J3" s="12" t="n">
         <v>117</v>
       </c>
     </row>
@@ -1311,7 +1547,7 @@
           <t>01 novembre 2026</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -1331,10 +1567,23 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>01 décembre 2026</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="J4" s="12" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1344,19 +1593,19 @@
           <t>01 décembre 2026</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>PaidPex</t>
+          <t>FundedCobra</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>cTrader</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -1364,11 +1613,24 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F5" s="10" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>11960</v>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>16 janvier 2027</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>594</v>
       </c>
     </row>
     <row r="6">
@@ -1377,19 +1639,19 @@
           <t>01 décembre 2026</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Lux Trading Firm</t>
+          <t>The5ers Crypto</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>cTrader, TradingView</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -1397,32 +1659,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>4995</v>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>01 février 2027</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>117</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>01 décembre 2026</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
+          <t>01 janvier 2027</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Elysium Forex</t>
+          <t>PaidPex</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>cTrader</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -1430,32 +1705,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F7" s="10" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>4000</v>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>01 février 2027</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>11960</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>01 décembre 2026</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
+          <t>01 janvier 2027</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Hydra Futures</t>
+          <t>Lux Trading Firm</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>cTrader, DXtrade, Volumetrica</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -1463,32 +1751,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>1980</v>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>01 février 2027</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>4995</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>01 décembre 2026</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
+          <t>01 janvier 2027</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>The5ers Crypto</t>
+          <t>The Whale Order</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>cTrader, TradingView</t>
+          <t>DXtrade</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -1496,32 +1797,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>120000</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>117</v>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>01 février 2027</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>14000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>01 décembre 2026</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
+          <t>01 janvier 2027</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Real Trader Fund</t>
+          <t>Hydra Futures</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>cTrader, DXtrade, Volumetrica</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1529,32 +1843,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>360</v>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>01 janvier 2027</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>1980</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>01 décembre 2026</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
+          <t>01 février 2027</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Thetradercapital</t>
+          <t>Upcomers</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>cTrader, Match-Trader, TradeLocker, DXtr</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1562,32 +1889,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>55</v>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>25 février 2027</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>30795</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
+          <t>01 février 2027</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Upcomers</t>
+          <t>NairaFunded</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader, TradeLocker, DXtr</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1595,27 +1935,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>30795</v>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>16 mars 2027</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>58000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
+          <t>01 février 2027</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>NairaProp</t>
+          <t>Elysium Forex</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -1628,32 +1981,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>135000</v>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>01 février 2027</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>4000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
+          <t>01 février 2027</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>The Whale Order</t>
+          <t>XLTrade</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>DXtrade</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1661,27 +2027,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>14000</v>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>3168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>NairaFunded</t>
+          <t>NairaProp</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -1694,20 +2073,33 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>58000</v>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>135000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -1727,27 +2119,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>09 avril 2027</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="n">
         <v>1400000</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="J16" s="12" t="n">
         <v>11200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>XLTrade</t>
+          <t>Funded Traders Pro</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
@@ -1760,32 +2165,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G17" s="10" t="n">
-        <v>3168</v>
+      <c r="J17" s="12" t="n">
+        <v>3500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Funded Traders Pro</t>
+          <t>IQ Capital</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MetaTrader 5, NinjaTrader, Tradovate, Qu</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1793,32 +2211,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G18" s="10" t="n">
-        <v>3500</v>
+      <c r="J18" s="12" t="n">
+        <v>4750</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>IQ Capital</t>
+          <t>Funded Trader Markets</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, NinjaTrader, Tradovate, Qu</t>
+          <t>cTrader, Match-Trader, TradeLocker</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1826,32 +2257,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>19 mars 2027</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G19" s="10" t="n">
-        <v>4750</v>
+      <c r="J19" s="12" t="n">
+        <v>5436</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Funded Trader Markets</t>
+          <t>Space Funded</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader, TradeLocker</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1859,32 +2303,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G20" s="10" t="n">
-        <v>5436</v>
+      <c r="J20" s="12" t="n">
+        <v>5696</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Space Funded</t>
+          <t>IF Crypto</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>cTrader, Match-Trader</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1892,32 +2349,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G21" s="10" t="n">
-        <v>5696</v>
+      <c r="J21" s="12" t="n">
+        <v>7390</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>IF Crypto</t>
+          <t>Instant Funding</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader</t>
+          <t>MetaTrader 5, cTrader, Match-Trader</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1925,32 +2395,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>28 mars 2027</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="J22" s="12" t="n">
         <v>7390</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Instant Funding</t>
+          <t>Kingdom Wealth Funding</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, Match-Trader</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1958,32 +2441,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G23" s="10" t="n">
-        <v>7390</v>
+      <c r="J23" s="12" t="n">
+        <v>8500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Kingdom Wealth Funding</t>
+          <t>The Proven Trader</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1991,32 +2487,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G24" s="10" t="n">
-        <v>8500</v>
+      <c r="J24" s="12" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>The Proven Trader</t>
+          <t>Sway Funded</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>cTrader</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2024,32 +2533,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>25 avril 2027</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G25" s="10" t="n">
-        <v>3000</v>
+      <c r="J25" s="12" t="n">
+        <v>4945</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Sway Funded</t>
+          <t>Instant Funding Pakistan</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>cTrader</t>
+          <t>cTrader, Match-Trader</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -2057,32 +2579,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n">
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G26" s="10" t="n">
-        <v>4945</v>
+      <c r="J26" s="12" t="n">
+        <v>4990</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Instant Funding Pakistan</t>
+          <t>Get Leveraged</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader</t>
+          <t>cTrader</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -2090,32 +2625,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>01 mai 2027</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G27" s="10" t="n">
-        <v>4990</v>
+      <c r="J27" s="12" t="n">
+        <v>2996</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Get Leveraged</t>
+          <t>Leveraged</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>cTrader</t>
+          <t>MetaTrader 5, cTrader</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -2123,32 +2671,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>01 mai 2027</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="J28" s="12" t="n">
         <v>2996</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Leveraged</t>
+          <t>We Fund Traders</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader</t>
+          <t>cTrader, Match-Trader, DXtrade</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -2156,32 +2717,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F29" s="10" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>2996</v>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>925000</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>6550</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>We Fund Traders</t>
+          <t>Pro Traders Fund</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader, DXtrade</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2189,27 +2763,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>925000</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <v>6550</v>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>07 avril 2027</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>900000</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>4197</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Pro Traders Fund</t>
+          <t>Mainet Funded</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
@@ -2222,32 +2809,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>900000</v>
-      </c>
-      <c r="G31" s="10" t="n">
-        <v>4197</v>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>10 avril 2027</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>700000</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>2975</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Mainet Funded</t>
+          <t>Fintokei</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>MetaTrader 5, cTrader, TradingView</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2255,32 +2855,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>04 avril 2027</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="n">
         <v>700000</v>
       </c>
-      <c r="G32" s="10" t="n">
-        <v>2975</v>
+      <c r="J32" s="12" t="n">
+        <v>2933</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Fintokei</t>
+          <t>Fill88</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, TradingView</t>
+          <t>MetaTrader 5, cTrader, Match-Trader</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2288,32 +2901,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>700000</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>2933</v>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>10 avril 2027</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>640000</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>2885</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Fill88</t>
+          <t>TTT Markets</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, Match-Trader</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2321,32 +2947,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>640000</v>
-      </c>
-      <c r="G34" s="10" t="n">
-        <v>2885</v>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>10 avril 2027</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>2994</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>TTT Markets</t>
+          <t>Eightcap Challenges</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MetaTrader 5, TradeLocker, TradingView</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2354,32 +2993,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F35" s="10" t="n">
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="n">
         <v>600000</v>
       </c>
-      <c r="G35" s="10" t="n">
-        <v>2994</v>
+      <c r="J35" s="12" t="n">
+        <v>3594</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Eightcap Challenges</t>
+          <t>ADN Broker</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, TradeLocker, TradingView</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2387,32 +3039,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G36" s="10" t="n">
-        <v>3594</v>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>50000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>ADN Broker</t>
+          <t>Hola Prime</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>cTrader, Match-Trader, TradeLocker</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2420,32 +3085,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>19 mars 2027</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G37" s="10" t="n">
-        <v>50000</v>
+      <c r="J37" s="12" t="n">
+        <v>1236</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Hola Prime</t>
+          <t>E8 Perpetuals</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader, TradeLocker</t>
+          <t>MetaTrader 5, cTrader, TradeLocker</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2453,32 +3131,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G38" s="10" t="n">
-        <v>1236</v>
+      <c r="J38" s="12" t="n">
+        <v>1300</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>E8 Perpetuals</t>
+          <t>E8 Markets</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, TradeLocker</t>
+          <t>MetaTrader 5, cTrader, Match-Trader, Tra</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2486,32 +3177,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F39" s="10" t="n">
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>19 mars 2027</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G39" s="10" t="n">
+      <c r="J39" s="12" t="n">
         <v>1300</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>E8 Markets</t>
+          <t>Foxx Funded</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, Match-Trader, Tra</t>
+          <t>MetaTrader 5, cTrader</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -2519,32 +3223,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F40" s="10" t="n">
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G40" s="10" t="n">
-        <v>1300</v>
+      <c r="J40" s="12" t="n">
+        <v>1990</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Foxx Funded</t>
+          <t>Quantum Funding</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader</t>
+          <t>cTrader</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -2552,32 +3269,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F41" s="10" t="n">
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G41" s="10" t="n">
-        <v>1990</v>
+      <c r="J41" s="12" t="n">
+        <v>2145</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Quantum Funding</t>
+          <t>Core Funded</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>cTrader</t>
+          <t>cTrader, Match-Trader</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -2585,32 +3315,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F42" s="10" t="n">
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G42" s="10" t="n">
-        <v>2145</v>
+      <c r="J42" s="12" t="n">
+        <v>1695</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Core Funded</t>
+          <t>TrioFunded</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -2618,32 +3361,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F43" s="10" t="n">
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G43" s="10" t="n">
-        <v>1695</v>
+      <c r="J43" s="12" t="n">
+        <v>2104</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>TrioFunded</t>
+          <t>IC Funded</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MetaTrader 5, cTrader</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2651,32 +3407,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G44" s="10" t="n">
-        <v>2104</v>
+      <c r="J44" s="12" t="n">
+        <v>2495</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>IC Funded</t>
+          <t>Vertex Funding</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader</t>
+          <t>cTrader, Match-Trader, DXtrade</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2684,27 +3453,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F45" s="10" t="n">
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G45" s="10" t="n">
-        <v>2495</v>
+      <c r="J45" s="12" t="n">
+        <v>2525</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Vertex Funding</t>
+          <t>FNC Funding</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -2717,27 +3499,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>01 mai 2027</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G46" s="10" t="n">
-        <v>2525</v>
+      <c r="J46" s="12" t="n">
+        <v>2625</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>FNC Funding</t>
+          <t>Blink Funding</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -2750,32 +3545,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F47" s="10" t="n">
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G47" s="10" t="n">
-        <v>2625</v>
+      <c r="J47" s="12" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Blink Funding</t>
+          <t>SFX Funded</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader, DXtrade</t>
+          <t>Match-Trader</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2783,32 +3591,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G48" s="10" t="n">
-        <v>1800</v>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>10 avril 2027</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>495000</v>
+      </c>
+      <c r="J48" s="12" t="n">
+        <v>2125</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>SFX Funded</t>
+          <t>XPIPS</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Match-Trader</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2816,32 +3637,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F49" s="10" t="n">
-        <v>495000</v>
-      </c>
-      <c r="G49" s="10" t="n">
-        <v>2125</v>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>400000</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>1596</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>XPIPS</t>
+          <t>Hex Funded</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2849,32 +3683,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G50" s="10" t="n">
-        <v>1596</v>
+      <c r="J50" s="12" t="n">
+        <v>1908</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Hex Funded</t>
+          <t>Blue Guardian</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>MetaTrader 5, Match-Trader, TradeLocker,</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2882,32 +3729,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F51" s="10" t="n">
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I51" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G51" s="10" t="n">
-        <v>1908</v>
+      <c r="J51" s="12" t="n">
+        <v>1472</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B52" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Blue Guardian</t>
+          <t>FTMO</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, Match-Trader, TradeLocker,</t>
+          <t>MetaTrader 5, cTrader, TradingView</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -2915,27 +3775,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F52" s="10" t="n">
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G52" s="10" t="n">
-        <v>1472</v>
+      <c r="J52" s="12" t="n">
+        <v>1996</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>FTMO</t>
+          <t>FTMO Crypto</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -2948,32 +3821,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F53" s="10" t="n">
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I53" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G53" s="10" t="n">
+      <c r="J53" s="12" t="n">
         <v>1996</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>FTMO Crypto</t>
+          <t>TradersFlow</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, TradingView</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -2981,32 +3867,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F54" s="10" t="n">
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G54" s="10" t="n">
-        <v>1996</v>
+      <c r="J54" s="12" t="n">
+        <v>2018</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>TradersFlow</t>
+          <t>The Trading Pit</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -3014,32 +3913,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F55" s="10" t="n">
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I55" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G55" s="10" t="n">
-        <v>2018</v>
+      <c r="J55" s="12" t="n">
+        <v>2276</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>The Trading Pit</t>
+          <t>FTMO US</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>MetaTrader 5, TradingView</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -3047,32 +3959,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F56" s="10" t="n">
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G56" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G56" s="10" t="n">
-        <v>2276</v>
+      <c r="J56" s="12" t="n">
+        <v>2298</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>FTMO US</t>
+          <t>Ultimate Traders</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, TradingView</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3080,32 +4005,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F57" s="10" t="n">
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I57" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G57" s="10" t="n">
-        <v>2298</v>
+      <c r="J57" s="12" t="n">
+        <v>1798</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Ultimate Traders</t>
+          <t>BrightFunded</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>cTrader, DXtrade</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -3113,32 +4051,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F58" s="10" t="n">
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G58" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>10 avril 2027</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G58" s="10" t="n">
-        <v>1798</v>
+      <c r="J58" s="12" t="n">
+        <v>1894</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>BrightFunded</t>
+          <t>NEOM Funded</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>cTrader, DXtrade</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -3146,32 +4097,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F59" s="10" t="n">
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I59" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G59" s="10" t="n">
-        <v>1894</v>
+      <c r="J59" s="12" t="n">
+        <v>1940</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>NEOM Funded</t>
+          <t>NYS Markets</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MetaTrader 5, Quantower, TradingView</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -3179,32 +4143,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F60" s="10" t="n">
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I60" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G60" s="10" t="n">
-        <v>1940</v>
+      <c r="J60" s="12" t="n">
+        <v>1974</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>NYS Markets</t>
+          <t>Quant Funded</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, Quantower, TradingView</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -3212,32 +4189,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F61" s="10" t="n">
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G61" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I61" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G61" s="10" t="n">
-        <v>1974</v>
+      <c r="J61" s="12" t="n">
+        <v>1996</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Quant Funded</t>
+          <t>Audacity Capital</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MetaTrader 5, DXtrade</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -3245,32 +4235,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F62" s="10" t="n">
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G62" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I62" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G62" s="10" t="n">
-        <v>1996</v>
+      <c r="J62" s="12" t="n">
+        <v>2098</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Audacity Capital</t>
+          <t>thePropTrade</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, DXtrade</t>
+          <t>cTrader, TradeLocker, Rithmic</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -3278,32 +4281,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F63" s="10" t="n">
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G63" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>10 avril 2027</t>
+        </is>
+      </c>
+      <c r="I63" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G63" s="10" t="n">
-        <v>2098</v>
+      <c r="J63" s="12" t="n">
+        <v>2116</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>thePropTrade</t>
+          <t>LegionFunding</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>cTrader, TradeLocker, Rithmic</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3311,32 +4327,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F64" s="10" t="n">
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G64" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G64" s="10" t="n">
+      <c r="J64" s="12" t="n">
         <v>2116</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>LegionFunding</t>
+          <t>WSFunded</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MetaTrader 5, cTrader, Match-Trader</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -3344,32 +4373,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F65" s="10" t="n">
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I65" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G65" s="10" t="n">
-        <v>2116</v>
+      <c r="J65" s="12" t="n">
+        <v>2236</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>WSFunded</t>
+          <t>Texaris</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, Match-Trader</t>
+          <t>TradeLocker, TradingView</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -3377,32 +4419,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F66" s="10" t="n">
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G66" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I66" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G66" s="10" t="n">
-        <v>2236</v>
+      <c r="J66" s="12" t="n">
+        <v>2796</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B67" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Texaris</t>
+          <t>Atlas Funded</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>TradeLocker, TradingView</t>
+          <t>MetaTrader 5, TradeLocker, Rithmic</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3410,32 +4465,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F67" s="10" t="n">
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G67" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>01 mai 2027</t>
+        </is>
+      </c>
+      <c r="I67" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G67" s="10" t="n">
-        <v>2796</v>
+      <c r="J67" s="12" t="n">
+        <v>1182</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Atlas Funded</t>
+          <t>AquaFunded</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, TradeLocker, Rithmic</t>
+          <t>MetaTrader 5, cTrader, TradeLocker, Rith</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3443,32 +4511,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F68" s="10" t="n">
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G68" s="15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>19 avril 2027</t>
+        </is>
+      </c>
+      <c r="I68" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G68" s="10" t="n">
-        <v>1182</v>
+      <c r="J68" s="12" t="n">
+        <v>1354</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B69" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>AquaFunded</t>
+          <t>Orion Funded</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, TradeLocker, Rith</t>
+          <t>cTrader, Match-Trader</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3476,32 +4557,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F69" s="10" t="n">
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G69" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>01 mai 2027</t>
+        </is>
+      </c>
+      <c r="I69" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G69" s="10" t="n">
-        <v>1354</v>
+      <c r="J69" s="12" t="n">
+        <v>1478</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Orion Funded</t>
+          <t>Get Crypto Funded</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader</t>
+          <t>MetaTrader 5, cTrader, Match-Trader</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -3509,32 +4603,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F70" s="10" t="n">
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>25 avril 2027</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G70" s="10" t="n">
-        <v>1478</v>
+      <c r="J70" s="12" t="n">
+        <v>1648</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Get Crypto Funded</t>
+          <t>Funding Pips</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, Match-Trader</t>
+          <t>cTrader, Match-Trader</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -3542,32 +4649,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F71" s="10" t="n">
-        <v>400000</v>
-      </c>
-      <c r="G71" s="10" t="n">
-        <v>1648</v>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>1332</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Funding Pips</t>
+          <t>Evercrest Funding</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader</t>
+          <t>MetaTrader 5, TradeLocker</t>
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -3575,27 +4695,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F72" s="10" t="n">
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I72" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G72" s="10" t="n">
-        <v>1332</v>
+      <c r="J72" s="12" t="n">
+        <v>1437</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B73" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Evercrest Funding</t>
+          <t>Clarity Traders</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -3608,32 +4741,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F73" s="10" t="n">
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>10 avril 2027</t>
+        </is>
+      </c>
+      <c r="I73" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G73" s="10" t="n">
-        <v>1437</v>
+      <c r="J73" s="12" t="n">
+        <v>1399</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Clarity Traders</t>
+          <t>Exclusive Funded Programme</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, TradeLocker</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -3641,27 +4787,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F74" s="10" t="n">
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>07 avril 2027</t>
+        </is>
+      </c>
+      <c r="I74" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G74" s="10" t="n">
-        <v>1399</v>
+      <c r="J74" s="12" t="n">
+        <v>1497</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B75" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Exclusive Funded Programme</t>
+          <t>Exclusive Markets Prop</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
@@ -3674,32 +4833,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F75" s="10" t="n">
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G75" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I75" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G75" s="10" t="n">
+      <c r="J75" s="12" t="n">
         <v>1497</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Exclusive Markets Prop</t>
+          <t>Prop Number One</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MetaTrader 5, cTrader, Match-Trader, Tra</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -3707,32 +4879,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F76" s="10" t="n">
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G76" s="10" t="n">
-        <v>1497</v>
+      <c r="J76" s="12" t="n">
+        <v>1592</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Prop Number One</t>
+          <t>Tradeify Crypto</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, Match-Trader, Tra</t>
+          <t>MetaTrader 5, DXtrade</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -3740,27 +4925,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F77" s="10" t="n">
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I77" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G77" s="10" t="n">
-        <v>1592</v>
+      <c r="J77" s="12" t="n">
+        <v>1740</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tradeify Crypto</t>
+          <t>Tradeify 247</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
@@ -3773,32 +4971,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F78" s="10" t="n">
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G78" s="10" t="n">
+      <c r="J78" s="12" t="n">
         <v>1740</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B79" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tradeify 247</t>
+          <t>Myfundedcapital</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, DXtrade</t>
+          <t>cTrader, Match-Trader, DXtrade</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -3806,32 +5017,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F79" s="10" t="n">
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I79" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G79" s="10" t="n">
-        <v>1740</v>
+      <c r="J79" s="12" t="n">
+        <v>1905</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B80" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Myfundedcapital</t>
+          <t>Htrader</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader, DXtrade</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -3839,32 +5063,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F80" s="10" t="n">
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>01 mai 2027</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G80" s="10" t="n">
-        <v>1905</v>
+      <c r="J80" s="12" t="n">
+        <v>798</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Htrader</t>
+          <t>Alpine Funded</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MetaTrader 5, cTrader</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -3872,32 +5109,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F81" s="10" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G81" s="10" t="n">
-        <v>798</v>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>200000</v>
+      </c>
+      <c r="J81" s="12" t="n">
+        <v>839</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Alpine Funded</t>
+          <t>We Copy Trade</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader</t>
+          <t>Match-Trader</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
@@ -3905,32 +5155,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F82" s="10" t="n">
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I82" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G82" s="10" t="n">
-        <v>839</v>
+      <c r="J82" s="12" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>We Copy Trade</t>
+          <t>EverFunded</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Match-Trader</t>
+          <t>MetaTrader 5, Match-Trader</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
@@ -3938,32 +5201,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F83" s="10" t="n">
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G83" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I83" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G83" s="10" t="n">
-        <v>2000</v>
+      <c r="J83" s="12" t="n">
+        <v>878</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>EverFunded</t>
+          <t>FunderPro</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, Match-Trader</t>
+          <t>cTrader, TradeLocker</t>
         </is>
       </c>
       <c r="E84" s="9" t="inlineStr">
@@ -3971,32 +5247,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F84" s="10" t="n">
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G84" s="15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>13 avril 2027</t>
+        </is>
+      </c>
+      <c r="I84" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G84" s="10" t="n">
-        <v>878</v>
+      <c r="J84" s="12" t="n">
+        <v>989</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>FunderPro</t>
+          <t>Funded Trading Plus</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>cTrader, TradeLocker</t>
+          <t>cTrader, Match-Trader, DXtrade</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -4004,32 +5293,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F85" s="10" t="n">
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I85" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G85" s="10" t="n">
-        <v>989</v>
+      <c r="J85" s="12" t="n">
+        <v>999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Funded Trading Plus</t>
+          <t>CK Capital</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader, DXtrade</t>
+          <t>TradeLocker</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
@@ -4037,32 +5339,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F86" s="10" t="n">
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>07 avril 2027</t>
+        </is>
+      </c>
+      <c r="I86" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G86" s="10" t="n">
-        <v>999</v>
+      <c r="J86" s="12" t="n">
+        <v>1056</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B87" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>CK Capital</t>
+          <t>Velotrade</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>TradeLocker</t>
+          <t>DXtrade</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
@@ -4070,32 +5385,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F87" s="10" t="n">
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G87" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I87" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G87" s="10" t="n">
-        <v>1056</v>
+      <c r="J87" s="12" t="n">
+        <v>1114</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B88" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Velotrade</t>
+          <t>Zeno Traders</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>DXtrade</t>
+          <t>cTrader, TradingView</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
@@ -4103,32 +5431,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F88" s="10" t="n">
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I88" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G88" s="10" t="n">
-        <v>1114</v>
+      <c r="J88" s="12" t="n">
+        <v>749</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B89" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>FundedCobra</t>
+          <t>T4TCapital</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MetaTrader 5, cTrader</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
@@ -4136,32 +5477,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F89" s="10" t="n">
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G89" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I89" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G89" s="10" t="n">
-        <v>594</v>
+      <c r="J89" s="12" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Zeno Traders</t>
+          <t>Funded Roll</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>cTrader, TradingView</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
@@ -4169,32 +5523,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F90" s="10" t="n">
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I90" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G90" s="10" t="n">
-        <v>749</v>
+      <c r="J90" s="12" t="n">
+        <v>899</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B91" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>T4TCapital</t>
+          <t>NowTradeFunded</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader</t>
+          <t>cTrader</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
@@ -4202,32 +5569,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F91" s="10" t="n">
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G91" s="15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>22 avril 2027</t>
+        </is>
+      </c>
+      <c r="I91" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G91" s="10" t="n">
-        <v>800</v>
+      <c r="J91" s="12" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Funded Roll</t>
+          <t>Cyber Funded</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MetaTrader 5, cTrader, Match-Trader, Tra</t>
         </is>
       </c>
       <c r="E92" s="9" t="inlineStr">
@@ -4235,32 +5615,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F92" s="10" t="n">
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I92" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G92" s="10" t="n">
-        <v>899</v>
+      <c r="J92" s="12" t="n">
+        <v>1038</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B93" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>NowTradeFunded</t>
+          <t>NextGen Funding</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>cTrader</t>
+          <t>MetaTrader 5, cTrader</t>
         </is>
       </c>
       <c r="E93" s="9" t="inlineStr">
@@ -4268,32 +5661,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F93" s="10" t="n">
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G93" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I93" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G93" s="10" t="n">
-        <v>900</v>
+      <c r="J93" s="12" t="n">
+        <v>1178</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B94" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Cyber Funded</t>
+          <t>Crypto Fund Trader</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader, Match-Trader, Tra</t>
+          <t>MetaTrader 5, Match-Trader</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
@@ -4301,32 +5707,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F94" s="10" t="n">
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>10 avril 2027</t>
+        </is>
+      </c>
+      <c r="I94" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G94" s="10" t="n">
-        <v>1038</v>
+      <c r="J94" s="12" t="n">
+        <v>1250</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B95" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>NextGen Funding</t>
+          <t>Monevis</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, cTrader</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
@@ -4334,32 +5753,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F95" s="10" t="n">
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G95" s="15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>13 avril 2027</t>
+        </is>
+      </c>
+      <c r="I95" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G95" s="10" t="n">
-        <v>1178</v>
+      <c r="J95" s="12" t="n">
+        <v>770</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Crypto Fund Trader</t>
+          <t>FX2 Funding</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, Match-Trader</t>
+          <t>cTrader, DXtrade</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr">
@@ -4367,32 +5799,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F96" s="10" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G96" s="10" t="n">
-        <v>1250</v>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>190000</v>
+      </c>
+      <c r="J96" s="12" t="n">
+        <v>1055</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B97" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Monevis</t>
+          <t>Ment Funding</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>cTrader, DXtrade</t>
         </is>
       </c>
       <c r="E97" s="9" t="inlineStr">
@@ -4400,32 +5845,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F97" s="10" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G97" s="10" t="n">
-        <v>770</v>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G97" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>190000</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>7451</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>FX2 Funding</t>
+          <t>Leveraged Crypto</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>cTrader, DXtrade</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -4433,32 +5891,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F98" s="10" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G98" s="10" t="n">
-        <v>1055</v>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G98" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>980</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B99" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Ment Funding</t>
+          <t>ArroxFund</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>cTrader, DXtrade</t>
+          <t>cTrader, Match-Trader</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
@@ -4466,32 +5937,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F99" s="10" t="n">
-        <v>190000</v>
-      </c>
-      <c r="G99" s="10" t="n">
-        <v>7451</v>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G99" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>708</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B100" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Leveraged Crypto</t>
+          <t>Real Trader Fund</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E100" s="9" t="inlineStr">
@@ -4499,32 +5983,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F100" s="10" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G100" s="10" t="n">
-        <v>980</v>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J100" s="12" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B101" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>ArroxFund</t>
+          <t>Funded Index</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader</t>
+          <t>cTrader, DXtrade</t>
         </is>
       </c>
       <c r="E101" s="9" t="inlineStr">
@@ -4532,32 +6029,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F101" s="10" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G101" s="10" t="n">
-        <v>708</v>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G101" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>352</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B102" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Funded Index</t>
+          <t>Propanium</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>cTrader, DXtrade</t>
+          <t>cTrader, TradeLocker</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
@@ -4565,32 +6075,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F102" s="10" t="n">
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G102" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>16 mars 2027</t>
+        </is>
+      </c>
+      <c r="I102" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G102" s="10" t="n">
-        <v>352</v>
+      <c r="J102" s="12" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B103" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Propanium</t>
+          <t>Pipcy</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>cTrader, TradeLocker</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
@@ -4598,32 +6121,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F103" s="10" t="n">
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G103" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I103" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G103" s="10" t="n">
-        <v>360</v>
+      <c r="J103" s="12" t="n">
+        <v>459</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B104" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Pipcy</t>
+          <t>Paid To Trade</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>Match-Trader</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
@@ -4631,32 +6167,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F104" s="10" t="n">
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I104" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G104" s="10" t="n">
-        <v>459</v>
+      <c r="J104" s="12" t="n">
+        <v>699</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B105" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Paid To Trade</t>
+          <t>Capital Mint Markets</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Match-Trader</t>
+          <t>MetaTrader 5, Rithmic</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
@@ -4664,32 +6213,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F105" s="10" t="n">
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G105" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I105" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G105" s="10" t="n">
+      <c r="J105" s="12" t="n">
         <v>699</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B106" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Capital Mint Markets</t>
+          <t>HUMBPROP</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5, Rithmic</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
@@ -4697,32 +6259,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F106" s="10" t="n">
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G106" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I106" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G106" s="10" t="n">
-        <v>699</v>
+      <c r="J106" s="12" t="n">
+        <v>239</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B107" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>HUMBPROP</t>
+          <t>Bold Fund</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>TradeLocker</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -4730,32 +6305,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F107" s="10" t="n">
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G107" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I107" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G107" s="10" t="n">
-        <v>239</v>
+      <c r="J107" s="12" t="n">
+        <v>499</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B108" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Bold Fund</t>
+          <t>MasterFunders</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>TradeLocker</t>
+          <t>Match-Trader, TradingView</t>
         </is>
       </c>
       <c r="E108" s="9" t="inlineStr">
@@ -4763,32 +6351,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F108" s="10" t="n">
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G108" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I108" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G108" s="10" t="n">
-        <v>499</v>
+      <c r="J108" s="12" t="n">
+        <v>549</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B109" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>MasterFunders</t>
+          <t>Prop Funders</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Match-Trader, TradingView</t>
+          <t>cTrader, Match-Trader, DXtrade</t>
         </is>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -4796,32 +6397,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F109" s="10" t="n">
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G109" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I109" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G109" s="10" t="n">
-        <v>549</v>
+      <c r="J109" s="12" t="n">
+        <v>579</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B110" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Prop Funders</t>
+          <t>The Upside Funding</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>cTrader, Match-Trader, DXtrade</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -4829,32 +6443,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F110" s="10" t="n">
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I110" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G110" s="10" t="n">
-        <v>579</v>
+      <c r="J110" s="12" t="n">
+        <v>589</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B111" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>The Upside Funding</t>
+          <t>Key to Prop</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
@@ -4862,32 +6489,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F111" s="10" t="n">
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G111" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I111" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G111" s="10" t="n">
-        <v>589</v>
+      <c r="J111" s="12" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B112" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Key to Prop</t>
+          <t>Investabl</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>MT5</t>
+          <t>MetaTrader 5</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
@@ -4895,27 +6535,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F112" s="10" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G112" s="10" t="n">
-        <v>650</v>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G112" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>209</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B113" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Investabl</t>
+          <t>PropFunding</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
@@ -4928,27 +6581,40 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F113" s="10" t="n">
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G113" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I113" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="G113" s="10" t="n">
-        <v>209</v>
+      <c r="J113" s="12" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B114" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>PropFunding</t>
+          <t>Ifunds</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
@@ -4961,32 +6627,45 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F114" s="10" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G114" s="10" t="n">
-        <v>150</v>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I114" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J114" s="12" t="n">
+        <v>700</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B115" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Ifunds</t>
+          <t>Thetradercapital</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>MetaTrader 5</t>
+          <t>MT5</t>
         </is>
       </c>
       <c r="E115" s="9" t="inlineStr">
@@ -4994,20 +6673,33 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F115" s="10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G115" s="10" t="n">
-        <v>700</v>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G115" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I115" s="12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J115" s="12" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B116" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5027,20 +6719,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F116" s="10" t="n">
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G116" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I116" s="12" t="n">
         <v>2500000</v>
       </c>
-      <c r="G116" s="10" t="n">
+      <c r="J116" s="12" t="n">
         <v>48499</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B117" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5060,20 +6765,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F117" s="10" t="n">
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I117" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G117" s="10" t="n">
+      <c r="J117" s="12" t="n">
         <v>349</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B118" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5093,20 +6811,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F118" s="10" t="n">
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G118" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I118" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G118" s="10" t="n">
+      <c r="J118" s="12" t="n">
         <v>6500</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B119" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5126,20 +6857,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F119" s="10" t="n">
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G119" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G119" s="10" t="n">
+      <c r="J119" s="12" t="n">
         <v>4800</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B120" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5159,20 +6903,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F120" s="10" t="n">
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G120" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I120" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G120" s="10" t="n">
+      <c r="J120" s="12" t="n">
         <v>5040</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B121" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5192,20 +6949,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F121" s="10" t="n">
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G121" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I121" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G121" s="10" t="n">
+      <c r="J121" s="12" t="n">
         <v>5883</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B122" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5225,20 +6995,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F122" s="10" t="n">
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G122" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I122" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G122" s="10" t="n">
+      <c r="J122" s="12" t="n">
         <v>6150</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B123" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5258,20 +7041,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F123" s="10" t="n">
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G123" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G123" s="10" t="n">
+      <c r="J123" s="12" t="n">
         <v>6803</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B124" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5291,20 +7087,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F124" s="10" t="n">
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G124" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I124" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G124" s="10" t="n">
+      <c r="J124" s="12" t="n">
         <v>7920</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B125" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B125" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5324,20 +7133,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F125" s="10" t="n">
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>4 étapes+</t>
+        </is>
+      </c>
+      <c r="G125" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>16 mai 2027</t>
+        </is>
+      </c>
+      <c r="I125" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G125" s="10" t="n">
+      <c r="J125" s="12" t="n">
         <v>4500</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B126" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5357,20 +7179,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F126" s="10" t="n">
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G126" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I126" s="12" t="n">
         <v>925000</v>
       </c>
-      <c r="G126" s="10" t="n">
+      <c r="J126" s="12" t="n">
         <v>9250</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B127" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B127" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5390,20 +7225,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F127" s="10" t="n">
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G127" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I127" s="12" t="n">
         <v>800000</v>
       </c>
-      <c r="G127" s="10" t="n">
+      <c r="J127" s="12" t="n">
         <v>3600</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B128" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5423,20 +7271,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F128" s="10" t="n">
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G128" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>07 avril 2027</t>
+        </is>
+      </c>
+      <c r="I128" s="12" t="n">
         <v>600000</v>
       </c>
-      <c r="G128" s="10" t="n">
+      <c r="J128" s="12" t="n">
         <v>2360</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B129" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B129" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5456,20 +7317,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F129" s="10" t="n">
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G129" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I129" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G129" s="10" t="n">
+      <c r="J129" s="12" t="n">
         <v>4250</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B130" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5489,20 +7363,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F130" s="10" t="n">
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G130" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I130" s="12" t="n">
         <v>500000</v>
       </c>
-      <c r="G130" s="10" t="n">
+      <c r="J130" s="12" t="n">
         <v>2450</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B131" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B131" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5522,20 +7409,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F131" s="10" t="n">
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G131" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I131" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G131" s="10" t="n">
+      <c r="J131" s="12" t="n">
         <v>2625</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B132" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5555,20 +7455,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F132" s="10" t="n">
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G132" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I132" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G132" s="10" t="n">
+      <c r="J132" s="12" t="n">
         <v>1699</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B133" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B133" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5588,20 +7501,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F133" s="10" t="n">
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G133" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I133" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G133" s="10" t="n">
+      <c r="J133" s="12" t="n">
         <v>1940</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B134" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5621,20 +7547,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F134" s="10" t="n">
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G134" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I134" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G134" s="10" t="n">
+      <c r="J134" s="12" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B135" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5654,20 +7593,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F135" s="10" t="n">
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G135" s="15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>07 avril 2027</t>
+        </is>
+      </c>
+      <c r="I135" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G135" s="10" t="n">
+      <c r="J135" s="12" t="n">
         <v>1400</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B136" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5687,20 +7639,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F136" s="10" t="n">
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G136" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I136" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G136" s="10" t="n">
+      <c r="J136" s="12" t="n">
         <v>2097</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B137" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B137" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5720,20 +7685,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F137" s="10" t="n">
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G137" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I137" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G137" s="10" t="n">
+      <c r="J137" s="12" t="n">
         <v>1260</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B138" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5753,20 +7731,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F138" s="10" t="n">
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G138" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I138" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G138" s="10" t="n">
+      <c r="J138" s="12" t="n">
         <v>1450</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B139" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B139" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5786,20 +7777,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F139" s="10" t="n">
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G139" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I139" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G139" s="10" t="n">
+      <c r="J139" s="12" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B140" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B140" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5819,20 +7823,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F140" s="10" t="n">
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G140" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I140" s="12" t="n">
         <v>250000</v>
       </c>
-      <c r="G140" s="10" t="n">
+      <c r="J140" s="12" t="n">
         <v>1125</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B141" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B141" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5852,20 +7869,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F141" s="10" t="n">
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I141" s="12" t="n">
         <v>240000</v>
       </c>
-      <c r="G141" s="10" t="n">
+      <c r="J141" s="12" t="n">
         <v>1365</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B142" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5885,20 +7915,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F142" s="10" t="n">
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G142" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I142" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G142" s="10" t="n">
+      <c r="J142" s="12" t="n">
         <v>900</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B143" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B143" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5918,20 +7961,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F143" s="10" t="n">
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G143" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I143" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G143" s="10" t="n">
+      <c r="J143" s="12" t="n">
         <v>958</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B144" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5951,20 +8007,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F144" s="10" t="n">
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G144" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I144" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G144" s="10" t="n">
+      <c r="J144" s="12" t="n">
         <v>1976</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B145" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B145" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -5984,20 +8053,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F145" s="10" t="n">
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G145" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>04 avril 2027</t>
+        </is>
+      </c>
+      <c r="I145" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G145" s="10" t="n">
+      <c r="J145" s="12" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B146" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6017,20 +8099,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F146" s="10" t="n">
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G146" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H146" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I146" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G146" s="10" t="n">
+      <c r="J146" s="12" t="n">
         <v>718</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B147" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B147" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6050,20 +8145,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F147" s="10" t="n">
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G147" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H147" s="9" t="inlineStr">
+        <is>
+          <t>10 avril 2027</t>
+        </is>
+      </c>
+      <c r="I147" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G147" s="10" t="n">
+      <c r="J147" s="12" t="n">
         <v>899</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B148" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6083,20 +8191,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F148" s="10" t="n">
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G148" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I148" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G148" s="10" t="n">
+      <c r="J148" s="12" t="n">
         <v>949</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B149" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B149" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6116,20 +8237,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F149" s="10" t="n">
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G149" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I149" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G149" s="10" t="n">
+      <c r="J149" s="12" t="n">
         <v>999</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B150" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6149,20 +8283,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F150" s="10" t="n">
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>3 étapes</t>
+        </is>
+      </c>
+      <c r="G150" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I150" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G150" s="10" t="n">
+      <c r="J150" s="12" t="n">
         <v>799</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B151" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B151" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6182,20 +8329,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F151" s="10" t="n">
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G151" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I151" s="12" t="n">
         <v>125000</v>
       </c>
-      <c r="G151" s="10" t="n">
+      <c r="J151" s="12" t="n">
         <v>498</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B152" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B152" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6215,20 +8375,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F152" s="10" t="n">
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I152" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G152" s="10" t="n">
+      <c r="J152" s="12" t="n">
         <v>650</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B153" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B153" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6248,20 +8421,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F153" s="10" t="n">
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G153" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I153" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G153" s="10" t="n">
+      <c r="J153" s="12" t="n">
         <v>799</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B154" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B154" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6281,20 +8467,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F154" s="10" t="n">
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G154" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I154" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G154" s="10" t="n">
+      <c r="J154" s="12" t="n">
         <v>892</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B155" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B155" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6314,20 +8513,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F155" s="10" t="n">
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G155" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I155" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G155" s="10" t="n">
+      <c r="J155" s="12" t="n">
         <v>999</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B156" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6347,20 +8559,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F156" s="10" t="n">
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G156" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H156" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I156" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G156" s="10" t="n">
+      <c r="J156" s="12" t="n">
         <v>399</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B157" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B157" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6380,20 +8605,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F157" s="10" t="n">
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G157" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I157" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="G157" s="10" t="n">
+      <c r="J157" s="12" t="n">
         <v>580</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B158" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B158" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6413,20 +8651,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F158" s="10" t="n">
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I158" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="G158" s="10" t="n">
+      <c r="J158" s="12" t="n">
         <v>1980</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B159" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B159" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6446,20 +8697,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F159" s="10" t="n">
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G159" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H159" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I159" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="G159" s="10" t="n">
+      <c r="J159" s="12" t="n">
         <v>141</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B160" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B160" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6479,20 +8743,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F160" s="10" t="n">
+      <c r="F160" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G160" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H160" s="9" t="inlineStr">
+        <is>
+          <t>16 avril 2027</t>
+        </is>
+      </c>
+      <c r="I160" s="12" t="n">
         <v>25000</v>
       </c>
-      <c r="G160" s="10" t="n">
+      <c r="J160" s="12" t="n">
         <v>149</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B161" s="13" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B161" s="14" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
@@ -6512,20 +8789,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F161" s="10" t="n">
+      <c r="F161" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G161" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I161" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="G161" s="10" t="n">
+      <c r="J161" s="12" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B162" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6545,20 +8835,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F162" s="10" t="n">
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G162" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I162" s="12" t="n">
         <v>10000000</v>
       </c>
-      <c r="G162" s="10" t="n">
+      <c r="J162" s="12" t="n">
         <v>34000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B163" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6578,20 +8881,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F163" s="10" t="n">
+      <c r="F163" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G163" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I163" s="12" t="n">
         <v>1650000</v>
       </c>
-      <c r="G163" s="10" t="n">
+      <c r="J163" s="12" t="n">
         <v>2114</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B164" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6611,20 +8927,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F164" s="10" t="n">
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G164" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>19 mars 2027</t>
+        </is>
+      </c>
+      <c r="I164" s="12" t="n">
         <v>1650000</v>
       </c>
-      <c r="G164" s="10" t="n">
+      <c r="J164" s="12" t="n">
         <v>2114</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B165" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B165" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6644,20 +8973,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F165" s="10" t="n">
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G165" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I165" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G165" s="10" t="n">
+      <c r="J165" s="12" t="n">
         <v>2693</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B166" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B166" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6677,20 +9019,33 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="F166" s="10" t="n">
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G166" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I166" s="12" t="n">
         <v>1000000</v>
       </c>
-      <c r="G166" s="10" t="n">
+      <c r="J166" s="12" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B167" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B167" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6710,20 +9065,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F167" s="10" t="n">
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G167" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I167" s="12" t="n">
         <v>900000</v>
       </c>
-      <c r="G167" s="10" t="n">
+      <c r="J167" s="12" t="n">
         <v>672</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B168" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6743,20 +9111,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F168" s="10" t="n">
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G168" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I168" s="12" t="n">
         <v>900000</v>
       </c>
-      <c r="G168" s="10" t="n">
+      <c r="J168" s="12" t="n">
         <v>672</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B169" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B169" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6776,20 +9157,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F169" s="10" t="n">
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G169" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I169" s="12" t="n">
         <v>750000</v>
       </c>
-      <c r="G169" s="10" t="n">
+      <c r="J169" s="12" t="n">
         <v>1095</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B170" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6809,20 +9203,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F170" s="10" t="n">
+      <c r="F170" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G170" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I170" s="12" t="n">
         <v>750000</v>
       </c>
-      <c r="G170" s="10" t="n">
+      <c r="J170" s="12" t="n">
         <v>1402</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B171" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B171" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6842,20 +9249,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F171" s="10" t="n">
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G171" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I171" s="12" t="n">
         <v>750000</v>
       </c>
-      <c r="G171" s="10" t="n">
+      <c r="J171" s="12" t="n">
         <v>1445</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B172" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6875,20 +9295,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F172" s="10" t="n">
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G172" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H172" s="9" t="inlineStr">
+        <is>
+          <t>19 mars 2027</t>
+        </is>
+      </c>
+      <c r="I172" s="12" t="n">
         <v>750000</v>
       </c>
-      <c r="G172" s="10" t="n">
+      <c r="J172" s="12" t="n">
         <v>1625</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B173" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B173" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6908,20 +9341,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F173" s="10" t="n">
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G173" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I173" s="12" t="n">
         <v>750000</v>
       </c>
-      <c r="G173" s="10" t="n">
+      <c r="J173" s="12" t="n">
         <v>2321</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B174" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6941,20 +9387,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F174" s="10" t="n">
+      <c r="F174" s="9" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="G174" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="9" t="inlineStr">
+        <is>
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="I174" s="12" t="n">
         <v>600000</v>
       </c>
-      <c r="G174" s="10" t="n">
+      <c r="J174" s="12" t="n">
         <v>5196</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B175" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B175" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -6974,20 +9433,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F175" s="10" t="n">
+      <c r="F175" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G175" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H175" s="9" t="inlineStr">
+        <is>
+          <t>19 mars 2027</t>
+        </is>
+      </c>
+      <c r="I175" s="12" t="n">
         <v>450000</v>
       </c>
-      <c r="G175" s="10" t="n">
+      <c r="J175" s="12" t="n">
         <v>687</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B176" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B176" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7007,20 +9479,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F176" s="10" t="n">
+      <c r="F176" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G176" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H176" s="9" t="inlineStr">
+        <is>
+          <t>19 mars 2027</t>
+        </is>
+      </c>
+      <c r="I176" s="12" t="n">
         <v>450000</v>
       </c>
-      <c r="G176" s="10" t="n">
+      <c r="J176" s="12" t="n">
         <v>1077</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B177" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B177" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7040,20 +9525,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F177" s="10" t="n">
+      <c r="F177" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G177" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I177" s="12" t="n">
         <v>450000</v>
       </c>
-      <c r="G177" s="10" t="n">
+      <c r="J177" s="12" t="n">
         <v>1287</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B178" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B178" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7073,20 +9571,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F178" s="10" t="n">
+      <c r="F178" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G178" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I178" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G178" s="10" t="n">
+      <c r="J178" s="12" t="n">
         <v>1058</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B179" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B179" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7106,20 +9617,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F179" s="10" t="n">
+      <c r="F179" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G179" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H179" s="9" t="inlineStr">
+        <is>
+          <t>19 mars 2027</t>
+        </is>
+      </c>
+      <c r="I179" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="G179" s="10" t="n">
+      <c r="J179" s="12" t="n">
         <v>4840</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B180" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B180" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7139,20 +9663,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F180" s="10" t="n">
+      <c r="F180" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G180" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I180" s="12" t="n">
         <v>325000</v>
       </c>
-      <c r="G180" s="10" t="n">
+      <c r="J180" s="12" t="n">
         <v>3385</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B181" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B181" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7172,20 +9709,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F181" s="10" t="n">
+      <c r="F181" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G181" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I181" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G181" s="10" t="n">
+      <c r="J181" s="12" t="n">
         <v>398</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B182" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B182" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7205,20 +9755,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F182" s="10" t="n">
+      <c r="F182" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G182" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I182" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G182" s="10" t="n">
+      <c r="J182" s="12" t="n">
         <v>864</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B183" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B183" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7238,20 +9801,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F183" s="10" t="n">
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G183" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I183" s="12" t="n">
         <v>300000</v>
       </c>
-      <c r="G183" s="10" t="n">
+      <c r="J183" s="12" t="n">
         <v>864</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B184" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B184" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7271,20 +9847,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F184" s="10" t="n">
+      <c r="F184" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G184" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I184" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G184" s="10" t="n">
+      <c r="J184" s="12" t="n">
         <v>286</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B185" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B185" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7304,20 +9893,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F185" s="10" t="n">
+      <c r="F185" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G185" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I185" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G185" s="10" t="n">
+      <c r="J185" s="12" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B186" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B186" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7337,20 +9939,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F186" s="10" t="n">
+      <c r="F186" s="9" t="inlineStr">
+        <is>
+          <t>2 étapes</t>
+        </is>
+      </c>
+      <c r="G186" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H186" s="9" t="inlineStr">
+        <is>
+          <t>25 avril 2027</t>
+        </is>
+      </c>
+      <c r="I186" s="12" t="n">
         <v>200000</v>
       </c>
-      <c r="G186" s="10" t="n">
+      <c r="J186" s="12" t="n">
         <v>999</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B187" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B187" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7370,20 +9985,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F187" s="10" t="n">
+      <c r="F187" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G187" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I187" s="12" t="n">
         <v>150000</v>
       </c>
-      <c r="G187" s="10" t="n">
+      <c r="J187" s="12" t="n">
         <v>147</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B188" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B188" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7403,20 +10031,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F188" s="10" t="n">
+      <c r="F188" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G188" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I188" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="G188" s="10" t="n">
+      <c r="J188" s="12" t="n">
         <v>579</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B189" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B189" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7436,20 +10077,33 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F189" s="10" t="n">
+      <c r="F189" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G189" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I189" s="12" t="n">
         <v>72000</v>
       </c>
-      <c r="G189" s="10" t="n">
+      <c r="J189" s="12" t="n">
         <v>21720</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>01 janvier 2027</t>
-        </is>
-      </c>
-      <c r="B190" s="14" t="inlineStr">
+          <t>01 mars 2027</t>
+        </is>
+      </c>
+      <c r="B190" s="16" t="inlineStr">
         <is>
           <t>Futures</t>
         </is>
@@ -7469,10 +10123,23 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="F190" s="10" t="n">
+      <c r="F190" s="9" t="inlineStr">
+        <is>
+          <t>1 étape</t>
+        </is>
+      </c>
+      <c r="G190" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" s="9" t="inlineStr">
+        <is>
+          <t>01 avril 2027</t>
+        </is>
+      </c>
+      <c r="I190" s="12" t="n">
         <v>540</v>
       </c>
-      <c r="G190" s="10" t="n">
+      <c r="J190" s="12" t="n">
         <v>41994</v>
       </c>
     </row>
@@ -7491,7 +10158,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Graphiques</t>
         </is>
